--- a/static/datasets/flame_retardant_thesis_dataset.xlsx
+++ b/static/datasets/flame_retardant_thesis_dataset.xlsx
@@ -5,7 +5,7 @@
     <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1 - 國內含「阻燃」關鍵字之碩博士論文資料集" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
